--- a/spreadsheets/domains/cramps-phy_CRAMPS-PHY_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-phy_CRAMPS-PHY_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R0ea9ad1130b64937"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R85ff7e667e854c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rb7aaad18fa2947d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R594fea15a3854c3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R812f7f4d5fe4417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R4faaf956f48d40cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Rc704f045825d44f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R8fa3413b83ff4dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Ra6bb6ee5020f49b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="Rc6ea3f96900c4b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R8c017a27f8714f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R67aae9b69d16408e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R30ac8278e1504bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R5d2b8fe18e204f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="R183ea60953f14dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R50dbfeedc1c74ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R7f962146ffd64f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R687225ae7b6d4781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R9d3eb31688ef4c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R19040880acd844ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>look-elsewhere effect; theory-fashion clustering; shared detector pipelines; plot digitization error</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
